--- a/opioid_trends/data/top10_horserace_graph.xlsx
+++ b/opioid_trends/data/top10_horserace_graph.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E111"/>
+  <dimension ref="A1:F111"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="20.7109375" style="2" customWidth="1"/>
@@ -387,404 +387,466 @@
           <t>year</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Delaware</t>
+          <t>District of Columbia</t>
         </is>
       </c>
       <c r="B2" s="2">
-        <v>42095</v>
+        <v>45017</v>
       </c>
       <c r="C2">
-        <v>200</v>
+        <v>603</v>
       </c>
       <c r="D2">
-        <v>20.368838935443</v>
+        <v>88.26706716201619</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2015</t>
-        </is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F2">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Kentucky</t>
+          <t>West Virginia</t>
         </is>
       </c>
       <c r="B3" s="2">
-        <v>42095</v>
+        <v>44287</v>
       </c>
       <c r="C3">
-        <v>1172</v>
+        <v>1563</v>
       </c>
       <c r="D3">
-        <v>26.07839851931659</v>
+        <v>86.78275827031914</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2015</t>
-        </is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F3">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Massachusetts</t>
+          <t>District of Columbia</t>
         </is>
       </c>
       <c r="B4" s="2">
-        <v>42095</v>
+        <v>45383</v>
       </c>
       <c r="C4">
-        <v>1376</v>
+        <v>588</v>
       </c>
       <c r="D4">
-        <v>19.68005043585019</v>
+        <v>86.07136897390632</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2015</t>
-        </is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F4">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>New Hampshire</t>
+          <t>District of Columbia</t>
         </is>
       </c>
       <c r="B5" s="2">
-        <v>42095</v>
+        <v>44652</v>
       </c>
       <c r="C5">
-        <v>394</v>
+        <v>553</v>
       </c>
       <c r="D5">
-        <v>28.71353872501685</v>
+        <v>80.94807320164999</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2015</t>
-        </is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F5">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>New Mexico</t>
+          <t>West Virginia</t>
         </is>
       </c>
       <c r="B6" s="2">
-        <v>42095</v>
+        <v>45017</v>
       </c>
       <c r="C6">
-        <v>536</v>
+        <v>1372</v>
       </c>
       <c r="D6">
-        <v>25.4104787884132</v>
+        <v>76.17782747720911</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2015</t>
-        </is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F6">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>West Virginia</t>
         </is>
       </c>
       <c r="B7" s="2">
-        <v>42095</v>
+        <v>44652</v>
       </c>
       <c r="C7">
-        <v>2955</v>
+        <v>1366</v>
       </c>
       <c r="D7">
-        <v>25.10636645626314</v>
+        <v>75.844688289991</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2015</t>
-        </is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F7">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pennsylvania</t>
+          <t>District of Columbia</t>
         </is>
       </c>
       <c r="B8" s="2">
-        <v>42095</v>
+        <v>44287</v>
       </c>
       <c r="C8">
-        <v>2862</v>
+        <v>499</v>
       </c>
       <c r="D8">
-        <v>22.06520105006303</v>
+        <v>73.04355972445451</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2015</t>
-        </is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F8">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>West Virginia</t>
         </is>
       </c>
       <c r="B9" s="2">
-        <v>42095</v>
+        <v>45383</v>
       </c>
       <c r="C9">
-        <v>267</v>
+        <v>1232</v>
       </c>
       <c r="D9">
-        <v>24.45169142514898</v>
+        <v>68.40457977545309</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2015</t>
-        </is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F9">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>West Virginia</t>
+          <t>District of Columbia</t>
         </is>
       </c>
       <c r="B10" s="2">
-        <v>42095</v>
+        <v>43922</v>
       </c>
       <c r="C10">
-        <v>683</v>
+        <v>450</v>
       </c>
       <c r="D10">
-        <v>37.9223441449955</v>
+        <v>65.87094564329566</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2015</t>
-        </is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F10">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Wyoming</t>
+          <t>Delaware</t>
         </is>
       </c>
       <c r="B11" s="2">
-        <v>42095</v>
+        <v>45017</v>
       </c>
       <c r="C11">
-        <v>112</v>
+        <v>564</v>
       </c>
       <c r="D11">
-        <v>19.42282980225131</v>
+        <v>57.44012579794927</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2015</t>
-        </is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F11">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Connecticut</t>
+          <t>Tennessee</t>
         </is>
       </c>
       <c r="B12" s="2">
-        <v>42461</v>
+        <v>45017</v>
       </c>
       <c r="C12">
-        <v>869</v>
+        <v>3878</v>
       </c>
       <c r="D12">
-        <v>24.10320275813864</v>
+        <v>56.53475757770577</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2016</t>
-        </is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F12">
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>District of Columbia</t>
+          <t>Tennessee</t>
         </is>
       </c>
       <c r="B13" s="2">
-        <v>42461</v>
+        <v>44652</v>
       </c>
       <c r="C13">
-        <v>174</v>
+        <v>3819</v>
       </c>
       <c r="D13">
-        <v>25.47009898207432</v>
+        <v>55.67463620145908</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2016</t>
-        </is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F13">
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Kentucky</t>
+          <t>District of Columbia</t>
         </is>
       </c>
       <c r="B14" s="2">
-        <v>42461</v>
+        <v>42826</v>
       </c>
       <c r="C14">
-        <v>1291</v>
+        <v>375</v>
       </c>
       <c r="D14">
-        <v>28.72629051914481</v>
+        <v>54.89245470274638</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2016</t>
-        </is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="F14">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Massachusetts</t>
+          <t>Louisiana</t>
         </is>
       </c>
       <c r="B15" s="2">
-        <v>42461</v>
+        <v>44652</v>
       </c>
       <c r="C15">
-        <v>1889</v>
+        <v>2551</v>
       </c>
       <c r="D15">
-        <v>27.01716226258794</v>
+        <v>54.77416660493569</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2016</t>
-        </is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F15">
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Maryland</t>
+          <t>West Virginia</t>
         </is>
       </c>
       <c r="B16" s="2">
-        <v>42461</v>
+        <v>42826</v>
       </c>
       <c r="C16">
-        <v>1479</v>
+        <v>983</v>
       </c>
       <c r="D16">
-        <v>24.05447142372708</v>
+        <v>54.57930350590128</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2016</t>
-        </is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="F16">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>New Hampshire</t>
+          <t>Alaska</t>
         </is>
       </c>
       <c r="B17" s="2">
-        <v>42461</v>
+        <v>45383</v>
       </c>
       <c r="C17">
-        <v>430</v>
+        <v>390</v>
       </c>
       <c r="D17">
-        <v>31.33711079126205</v>
+        <v>52.99265847862154</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2016</t>
-        </is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F17">
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>District of Columbia</t>
         </is>
       </c>
       <c r="B18" s="2">
-        <v>42461</v>
+        <v>45748</v>
       </c>
       <c r="C18">
-        <v>3575</v>
+        <v>360</v>
       </c>
       <c r="D18">
-        <v>30.37403048431158</v>
+        <v>52.69675651463653</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2016</t>
-        </is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F18">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Pennsylvania</t>
+          <t>Kentucky</t>
         </is>
       </c>
       <c r="B19" s="2">
-        <v>42461</v>
+        <v>45017</v>
       </c>
       <c r="C19">
-        <v>3601</v>
+        <v>2341</v>
       </c>
       <c r="D19">
-        <v>27.76267958814709</v>
+        <v>52.09004345880559</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2016</t>
-        </is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F19">
+        <v>5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Kentucky</t>
         </is>
       </c>
       <c r="B20" s="2">
-        <v>42461</v>
+        <v>44287</v>
       </c>
       <c r="C20">
-        <v>328</v>
+        <v>2321</v>
       </c>
       <c r="D20">
-        <v>30.0380329117935</v>
+        <v>51.64501959328825</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2016</t>
-        </is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F20">
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -794,39 +856,45 @@
         </is>
       </c>
       <c r="B21" s="2">
-        <v>42461</v>
+        <v>43922</v>
       </c>
       <c r="C21">
-        <v>764</v>
+        <v>929</v>
       </c>
       <c r="D21">
-        <v>42.41972317244006</v>
+        <v>51.58105082093824</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2016</t>
-        </is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F21">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>District of Columbia</t>
+          <t>Kentucky</t>
         </is>
       </c>
       <c r="B22" s="2">
-        <v>42826</v>
+        <v>44652</v>
       </c>
       <c r="C22">
-        <v>375</v>
+        <v>2315</v>
       </c>
       <c r="D22">
-        <v>54.89245470274638</v>
+        <v>51.51151243363303</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2017</t>
-        </is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F22">
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -836,291 +904,333 @@
         </is>
       </c>
       <c r="B23" s="2">
-        <v>42826</v>
+        <v>44652</v>
       </c>
       <c r="C23">
-        <v>313</v>
+        <v>505</v>
       </c>
       <c r="D23">
-        <v>31.87723293396829</v>
+        <v>51.43131831199359</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2017</t>
-        </is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F23">
+        <v>6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Kentucky</t>
+          <t>Maine</t>
         </is>
       </c>
       <c r="B24" s="2">
-        <v>42826</v>
+        <v>45017</v>
       </c>
       <c r="C24">
-        <v>1580</v>
+        <v>697</v>
       </c>
       <c r="D24">
-        <v>35.15688537587049</v>
+        <v>51.36156033030567</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2017</t>
-        </is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F24">
+        <v>6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Massachusetts</t>
+          <t>Tennessee</t>
         </is>
       </c>
       <c r="B25" s="2">
-        <v>42826</v>
+        <v>44287</v>
       </c>
       <c r="C25">
-        <v>2168</v>
+        <v>3512</v>
       </c>
       <c r="D25">
-        <v>31.00752132625233</v>
+        <v>51.19908937929414</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2017</t>
-        </is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F25">
+        <v>4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Maryland</t>
+          <t>New Mexico</t>
         </is>
       </c>
       <c r="B26" s="2">
-        <v>42826</v>
+        <v>44652</v>
       </c>
       <c r="C26">
-        <v>2265</v>
+        <v>1067</v>
       </c>
       <c r="D26">
-        <v>36.8379836205151</v>
+        <v>50.58391952842702</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2017</t>
-        </is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F26">
+        <v>7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>New Hampshire</t>
+          <t>West Virginia</t>
         </is>
       </c>
       <c r="B27" s="2">
-        <v>42826</v>
+        <v>43191</v>
       </c>
       <c r="C27">
-        <v>447</v>
+        <v>898</v>
       </c>
       <c r="D27">
-        <v>32.5760198225445</v>
+        <v>49.85983168697798</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2017</t>
-        </is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="F27">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>Louisiana</t>
         </is>
       </c>
       <c r="B28" s="2">
-        <v>42826</v>
+        <v>45017</v>
       </c>
       <c r="C28">
-        <v>4974</v>
+        <v>2319</v>
       </c>
       <c r="D28">
-        <v>42.26025947663379</v>
+        <v>49.79274494584314</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2017</t>
-        </is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F28">
+        <v>7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Pennsylvania</t>
+          <t>Tennessee</t>
         </is>
       </c>
       <c r="B29" s="2">
-        <v>42826</v>
+        <v>45383</v>
       </c>
       <c r="C29">
-        <v>5220</v>
+        <v>3385</v>
       </c>
       <c r="D29">
-        <v>40.24470631772502</v>
+        <v>49.34764167110212</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2017</t>
-        </is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F29">
+        <v>4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Delaware</t>
         </is>
       </c>
       <c r="B30" s="2">
-        <v>42826</v>
+        <v>45383</v>
       </c>
       <c r="C30">
-        <v>339</v>
+        <v>473</v>
       </c>
       <c r="D30">
-        <v>31.04540596676219</v>
+        <v>48.1723040823227</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2017</t>
-        </is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F30">
+        <v>5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>West Virginia</t>
+          <t>Louisiana</t>
         </is>
       </c>
       <c r="B31" s="2">
-        <v>42826</v>
+        <v>44287</v>
       </c>
       <c r="C31">
-        <v>983</v>
+        <v>2225</v>
       </c>
       <c r="D31">
-        <v>54.57930350590128</v>
+        <v>47.77441030810737</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2017</t>
-        </is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F31">
+        <v>5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>District of Columbia</t>
+          <t>Ohio</t>
         </is>
       </c>
       <c r="B32" s="2">
-        <v>43191</v>
+        <v>44287</v>
       </c>
       <c r="C32">
-        <v>302</v>
+        <v>5582</v>
       </c>
       <c r="D32">
-        <v>44.20672352061175</v>
+        <v>47.42596871704259</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2018</t>
-        </is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F32">
+        <v>6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Delaware</t>
+          <t>West Virginia</t>
         </is>
       </c>
       <c r="B33" s="2">
-        <v>43191</v>
+        <v>43556</v>
       </c>
       <c r="C33">
-        <v>360</v>
+        <v>854</v>
       </c>
       <c r="D33">
-        <v>36.6639100837974</v>
+        <v>47.41681098071179</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2018</t>
-        </is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="F33">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Kentucky</t>
+          <t>Delaware</t>
         </is>
       </c>
       <c r="B34" s="2">
-        <v>43191</v>
+        <v>43922</v>
       </c>
       <c r="C34">
-        <v>1418</v>
+        <v>463</v>
       </c>
       <c r="D34">
-        <v>31.55219206517998</v>
+        <v>47.15386213555055</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2018</t>
-        </is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F34">
+        <v>3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Massachusetts</t>
+          <t>Nevada</t>
         </is>
       </c>
       <c r="B35" s="2">
-        <v>43191</v>
+        <v>45383</v>
       </c>
       <c r="C35">
-        <v>2166</v>
+        <v>1440</v>
       </c>
       <c r="D35">
-        <v>30.97891660178162</v>
+        <v>47.07054501807313</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2018</t>
-        </is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F35">
+        <v>6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Maryland</t>
+          <t>Delaware</t>
         </is>
       </c>
       <c r="B36" s="2">
-        <v>43191</v>
+        <v>44287</v>
       </c>
       <c r="C36">
-        <v>2410</v>
+        <v>460</v>
       </c>
       <c r="D36">
-        <v>39.1962651326452</v>
+        <v>46.8483295515189</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2018</t>
-        </is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F36">
+        <v>7</v>
       </c>
     </row>
     <row r="37">
@@ -1130,606 +1240,693 @@
         </is>
       </c>
       <c r="B37" s="2">
-        <v>43191</v>
+        <v>44652</v>
       </c>
       <c r="C37">
-        <v>404</v>
+        <v>634</v>
       </c>
       <c r="D37">
-        <v>29.77054572947417</v>
+        <v>46.71912374377877</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2018</t>
-        </is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F37">
+        <v>8</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>New Hampshire</t>
+          <t>Maryland</t>
         </is>
       </c>
       <c r="B38" s="2">
-        <v>43191</v>
+        <v>44287</v>
       </c>
       <c r="C38">
-        <v>473</v>
+        <v>2872</v>
       </c>
       <c r="D38">
-        <v>34.47082187038825</v>
+        <v>46.71023795060457</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2018</t>
-        </is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F38">
+        <v>8</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="B39" s="2">
-        <v>43191</v>
+        <v>45383</v>
       </c>
       <c r="C39">
-        <v>4418</v>
+        <v>3527</v>
       </c>
       <c r="D39">
-        <v>37.5363543159968</v>
+        <v>46.3021066080077</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2018</t>
-        </is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F39">
+        <v>7</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Pennsylvania</t>
+          <t>New Mexico</t>
         </is>
       </c>
       <c r="B40" s="2">
-        <v>43191</v>
+        <v>45017</v>
       </c>
       <c r="C40">
-        <v>4912</v>
+        <v>975</v>
       </c>
       <c r="D40">
-        <v>37.87011445070216</v>
+        <v>46.22241943787849</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2018</t>
-        </is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F40">
+        <v>8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>West Virginia</t>
+          <t>South Carolina</t>
         </is>
       </c>
       <c r="B41" s="2">
-        <v>43191</v>
+        <v>45017</v>
       </c>
       <c r="C41">
-        <v>898</v>
+        <v>2309</v>
       </c>
       <c r="D41">
-        <v>49.85983168697798</v>
+        <v>45.46257331553684</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2018</t>
-        </is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F41">
+        <v>9</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>District of Columbia</t>
+          <t>Alaska</t>
         </is>
       </c>
       <c r="B42" s="2">
-        <v>43556</v>
+        <v>45748</v>
       </c>
       <c r="C42">
-        <v>292</v>
+        <v>334</v>
       </c>
       <c r="D42">
-        <v>42.74292472853851</v>
+        <v>45.38345623553742</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F42">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Delaware</t>
+          <t>Nevada</t>
         </is>
       </c>
       <c r="B43" s="2">
-        <v>43556</v>
+        <v>45748</v>
       </c>
       <c r="C43">
-        <v>392</v>
+        <v>1386</v>
       </c>
       <c r="D43">
-        <v>39.92292431346828</v>
+        <v>45.30539957989539</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F43">
+        <v>3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Massachusetts</t>
+          <t>Oregon</t>
         </is>
       </c>
       <c r="B44" s="2">
-        <v>43556</v>
+        <v>45383</v>
       </c>
       <c r="C44">
-        <v>2217</v>
+        <v>1902</v>
       </c>
       <c r="D44">
-        <v>31.70833707578478</v>
+        <v>45.20846163591406</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F44">
+        <v>8</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Maryland</t>
+          <t>Louisiana</t>
         </is>
       </c>
       <c r="B45" s="2">
-        <v>43556</v>
+        <v>45383</v>
       </c>
       <c r="C45">
-        <v>2324</v>
+        <v>2079</v>
       </c>
       <c r="D45">
-        <v>37.79756023579562</v>
+        <v>44.63955012609223</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F45">
+        <v>9</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>New Hampshire</t>
+          <t>Ohio</t>
         </is>
       </c>
       <c r="B46" s="2">
-        <v>43556</v>
+        <v>44652</v>
       </c>
       <c r="C46">
-        <v>437</v>
+        <v>5213</v>
       </c>
       <c r="D46">
-        <v>31.84724980414306</v>
+        <v>44.29085899712343</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F46">
+        <v>9</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>New Jersey</t>
+          <t>Ohio</t>
         </is>
       </c>
       <c r="B47" s="2">
-        <v>43556</v>
+        <v>45017</v>
       </c>
       <c r="C47">
-        <v>2771</v>
+        <v>5206</v>
       </c>
       <c r="D47">
-        <v>30.00858563937022</v>
+        <v>44.2313853710003</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F47">
+        <v>10</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>New Mexico</t>
         </is>
       </c>
       <c r="B48" s="2">
-        <v>43556</v>
+        <v>45383</v>
       </c>
       <c r="C48">
-        <v>4110</v>
+        <v>933</v>
       </c>
       <c r="D48">
-        <v>34.91951476657919</v>
+        <v>44.23129983132372</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F48">
+        <v>10</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Pennsylvania</t>
+          <t>District of Columbia</t>
         </is>
       </c>
       <c r="B49" s="2">
-        <v>43556</v>
+        <v>43191</v>
       </c>
       <c r="C49">
-        <v>4379</v>
+        <v>302</v>
       </c>
       <c r="D49">
-        <v>33.76083696653599</v>
+        <v>44.20672352061175</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="F49">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>South Carolina</t>
         </is>
       </c>
       <c r="B50" s="2">
-        <v>43556</v>
+        <v>44652</v>
       </c>
       <c r="C50">
-        <v>345</v>
+        <v>2212</v>
       </c>
       <c r="D50">
-        <v>31.59488217856329</v>
+        <v>43.55271207187851</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F50">
+        <v>10</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>West Virginia</t>
+          <t>District of Columbia</t>
         </is>
       </c>
       <c r="B51" s="2">
         <v>43556</v>
       </c>
       <c r="C51">
-        <v>854</v>
+        <v>292</v>
       </c>
       <c r="D51">
-        <v>47.41681098071179</v>
+        <v>42.74292472853851</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
+      </c>
+      <c r="F51">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Connecticut</t>
+          <t>New Mexico</t>
         </is>
       </c>
       <c r="B52" s="2">
-        <v>43922</v>
+        <v>44287</v>
       </c>
       <c r="C52">
-        <v>1333</v>
+        <v>899</v>
       </c>
       <c r="D52">
-        <v>36.97303714223109</v>
+        <v>42.61944110220796</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2020</t>
-        </is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F52">
+        <v>9</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>District of Columbia</t>
+          <t>West Virginia</t>
         </is>
       </c>
       <c r="B53" s="2">
-        <v>43922</v>
+        <v>42461</v>
       </c>
       <c r="C53">
-        <v>450</v>
+        <v>764</v>
       </c>
       <c r="D53">
-        <v>65.87094564329566</v>
+        <v>42.41972317244006</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2020</t>
-        </is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F53">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Delaware</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="B54" s="2">
-        <v>43922</v>
+        <v>45748</v>
       </c>
       <c r="C54">
-        <v>463</v>
+        <v>3227</v>
       </c>
       <c r="D54">
-        <v>47.15386213555055</v>
+        <v>42.36373632663478</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2020</t>
-        </is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F54">
+        <v>4</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Kentucky</t>
+          <t>Ohio</t>
         </is>
       </c>
       <c r="B55" s="2">
-        <v>43922</v>
+        <v>42826</v>
       </c>
       <c r="C55">
-        <v>1501</v>
+        <v>4974</v>
       </c>
       <c r="D55">
-        <v>33.39904110707697</v>
+        <v>42.26025947663379</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2020</t>
-        </is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="F55">
+        <v>3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Massachusetts</t>
+          <t>Pennsylvania</t>
         </is>
       </c>
       <c r="B56" s="2">
-        <v>43922</v>
+        <v>44287</v>
       </c>
       <c r="C56">
-        <v>2244</v>
+        <v>5315</v>
       </c>
       <c r="D56">
-        <v>32.0945008561394</v>
+        <v>40.97712913385219</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2020</t>
-        </is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F56">
+        <v>10</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Maryland</t>
+          <t>West Virginia</t>
         </is>
       </c>
       <c r="B57" s="2">
-        <v>43922</v>
+        <v>45748</v>
       </c>
       <c r="C57">
-        <v>2373</v>
+        <v>729</v>
       </c>
       <c r="D57">
-        <v>38.59449674679131</v>
+        <v>40.47641124700105</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2020</t>
-        </is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F57">
+        <v>5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>Pennsylvania</t>
         </is>
       </c>
       <c r="B58" s="2">
-        <v>43922</v>
+        <v>42826</v>
       </c>
       <c r="C58">
-        <v>4410</v>
+        <v>5220</v>
       </c>
       <c r="D58">
-        <v>37.46838445757037</v>
+        <v>40.24470631772502</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2020</t>
-        </is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="F58">
+        <v>4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Pennsylvania</t>
+          <t>Delaware</t>
         </is>
       </c>
       <c r="B59" s="2">
-        <v>43922</v>
+        <v>43556</v>
       </c>
       <c r="C59">
-        <v>4699</v>
+        <v>392</v>
       </c>
       <c r="D59">
-        <v>36.22794539980649</v>
+        <v>39.92292431346828</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2020</t>
-        </is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="F59">
+        <v>3</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Tennessee</t>
+          <t>Arizona</t>
         </is>
       </c>
       <c r="B60" s="2">
-        <v>43922</v>
+        <v>45748</v>
       </c>
       <c r="C60">
-        <v>2354</v>
+        <v>2790</v>
       </c>
       <c r="D60">
-        <v>34.3173850794016</v>
+        <v>39.41121620611812</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2020</t>
-        </is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F60">
+        <v>6</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>West Virginia</t>
+          <t>Maryland</t>
         </is>
       </c>
       <c r="B61" s="2">
-        <v>43922</v>
+        <v>43191</v>
       </c>
       <c r="C61">
-        <v>929</v>
+        <v>2410</v>
       </c>
       <c r="D61">
-        <v>51.58105082093824</v>
+        <v>39.1962651326452</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2020</t>
-        </is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="F61">
+        <v>3</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>District of Columbia</t>
+          <t>New Mexico</t>
         </is>
       </c>
       <c r="B62" s="2">
-        <v>44287</v>
+        <v>45748</v>
       </c>
       <c r="C62">
-        <v>499</v>
+        <v>824</v>
       </c>
       <c r="D62">
-        <v>73.04355972445451</v>
+        <v>39.06387037621731</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2021</t>
-        </is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F62">
+        <v>7</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Delaware</t>
+          <t>Maryland</t>
         </is>
       </c>
       <c r="B63" s="2">
-        <v>44287</v>
+        <v>43922</v>
       </c>
       <c r="C63">
-        <v>460</v>
+        <v>2373</v>
       </c>
       <c r="D63">
-        <v>46.8483295515189</v>
+        <v>38.59449674679131</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2021</t>
-        </is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F63">
+        <v>4</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Kentucky</t>
+          <t>West Virginia</t>
         </is>
       </c>
       <c r="B64" s="2">
-        <v>44287</v>
+        <v>42095</v>
       </c>
       <c r="C64">
-        <v>2321</v>
+        <v>683</v>
       </c>
       <c r="D64">
-        <v>51.64501959328825</v>
+        <v>37.9223441449955</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2021</t>
-        </is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="F64">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Louisiana</t>
+          <t>Pennsylvania</t>
         </is>
       </c>
       <c r="B65" s="2">
-        <v>44287</v>
+        <v>43191</v>
       </c>
       <c r="C65">
-        <v>2225</v>
+        <v>4912</v>
       </c>
       <c r="D65">
-        <v>47.77441030810737</v>
+        <v>37.87011445070216</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2021</t>
-        </is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="F65">
+        <v>4</v>
       </c>
     </row>
     <row r="66">
@@ -1739,39 +1936,45 @@
         </is>
       </c>
       <c r="B66" s="2">
-        <v>44287</v>
+        <v>43556</v>
       </c>
       <c r="C66">
-        <v>2872</v>
+        <v>2324</v>
       </c>
       <c r="D66">
-        <v>46.71023795060457</v>
+        <v>37.79756023579562</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2021</t>
-        </is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="F66">
+        <v>4</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>New Mexico</t>
+          <t>Ohio</t>
         </is>
       </c>
       <c r="B67" s="2">
-        <v>44287</v>
+        <v>43191</v>
       </c>
       <c r="C67">
-        <v>899</v>
+        <v>4418</v>
       </c>
       <c r="D67">
-        <v>42.61944110220796</v>
+        <v>37.5363543159968</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2021</t>
-        </is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="F67">
+        <v>5</v>
       </c>
     </row>
     <row r="68">
@@ -1781,123 +1984,141 @@
         </is>
       </c>
       <c r="B68" s="2">
-        <v>44287</v>
+        <v>43922</v>
       </c>
       <c r="C68">
-        <v>5582</v>
+        <v>4410</v>
       </c>
       <c r="D68">
-        <v>47.42596871704259</v>
+        <v>37.46838445757037</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2021</t>
-        </is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F68">
+        <v>5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Pennsylvania</t>
+          <t>Connecticut</t>
         </is>
       </c>
       <c r="B69" s="2">
-        <v>44287</v>
+        <v>43922</v>
       </c>
       <c r="C69">
-        <v>5315</v>
+        <v>1333</v>
       </c>
       <c r="D69">
-        <v>40.97712913385219</v>
+        <v>36.97303714223109</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2021</t>
-        </is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F69">
+        <v>6</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Tennessee</t>
+          <t>Maryland</t>
         </is>
       </c>
       <c r="B70" s="2">
-        <v>44287</v>
+        <v>42826</v>
       </c>
       <c r="C70">
-        <v>3512</v>
+        <v>2265</v>
       </c>
       <c r="D70">
-        <v>51.19908937929414</v>
+        <v>36.8379836205151</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2021</t>
-        </is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="F70">
+        <v>5</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>West Virginia</t>
+          <t>Delaware</t>
         </is>
       </c>
       <c r="B71" s="2">
-        <v>44287</v>
+        <v>43191</v>
       </c>
       <c r="C71">
-        <v>1563</v>
+        <v>360</v>
       </c>
       <c r="D71">
-        <v>86.78275827031914</v>
+        <v>36.6639100837974</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2021</t>
-        </is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="F71">
+        <v>6</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>District of Columbia</t>
+          <t>Delaware</t>
         </is>
       </c>
       <c r="B72" s="2">
-        <v>44652</v>
+        <v>45748</v>
       </c>
       <c r="C72">
-        <v>553</v>
+        <v>356</v>
       </c>
       <c r="D72">
-        <v>80.94807320164999</v>
+        <v>36.25653330508855</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2022</t>
-        </is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F72">
+        <v>8</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Delaware</t>
+          <t>Pennsylvania</t>
         </is>
       </c>
       <c r="B73" s="2">
-        <v>44652</v>
+        <v>43922</v>
       </c>
       <c r="C73">
-        <v>505</v>
+        <v>4699</v>
       </c>
       <c r="D73">
-        <v>51.43131831199359</v>
+        <v>36.22794539980649</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2022</t>
-        </is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F73">
+        <v>7</v>
       </c>
     </row>
     <row r="74">
@@ -1907,186 +2128,213 @@
         </is>
       </c>
       <c r="B74" s="2">
-        <v>44652</v>
+        <v>42826</v>
       </c>
       <c r="C74">
-        <v>2315</v>
+        <v>1580</v>
       </c>
       <c r="D74">
-        <v>51.51151243363303</v>
+        <v>35.15688537587049</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2022</t>
-        </is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="F74">
+        <v>6</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Louisiana</t>
+          <t>Ohio</t>
         </is>
       </c>
       <c r="B75" s="2">
-        <v>44652</v>
+        <v>43556</v>
       </c>
       <c r="C75">
-        <v>2551</v>
+        <v>4110</v>
       </c>
       <c r="D75">
-        <v>54.77416660493569</v>
+        <v>34.91951476657919</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2022</t>
-        </is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="F75">
+        <v>5</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Maine</t>
+          <t>New Hampshire</t>
         </is>
       </c>
       <c r="B76" s="2">
-        <v>44652</v>
+        <v>43191</v>
       </c>
       <c r="C76">
-        <v>634</v>
+        <v>473</v>
       </c>
       <c r="D76">
-        <v>46.71912374377877</v>
+        <v>34.47082187038825</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2022</t>
-        </is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="F76">
+        <v>7</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>New Mexico</t>
+          <t>Tennessee</t>
         </is>
       </c>
       <c r="B77" s="2">
-        <v>44652</v>
+        <v>45748</v>
       </c>
       <c r="C77">
-        <v>1067</v>
+        <v>2361</v>
       </c>
       <c r="D77">
-        <v>50.58391952842702</v>
+        <v>34.41943337827832</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2022</t>
-        </is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F77">
+        <v>9</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>Tennessee</t>
         </is>
       </c>
       <c r="B78" s="2">
-        <v>44652</v>
+        <v>43922</v>
       </c>
       <c r="C78">
-        <v>5213</v>
+        <v>2354</v>
       </c>
       <c r="D78">
-        <v>44.29085899712343</v>
+        <v>34.3173850794016</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2022</t>
-        </is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F78">
+        <v>8</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>South Carolina</t>
+          <t>Pennsylvania</t>
         </is>
       </c>
       <c r="B79" s="2">
-        <v>44652</v>
+        <v>43556</v>
       </c>
       <c r="C79">
-        <v>2212</v>
+        <v>4379</v>
       </c>
       <c r="D79">
-        <v>43.55271207187851</v>
+        <v>33.76083696653599</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2022</t>
-        </is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="F79">
+        <v>6</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Tennessee</t>
+          <t>Kentucky</t>
         </is>
       </c>
       <c r="B80" s="2">
-        <v>44652</v>
+        <v>43922</v>
       </c>
       <c r="C80">
-        <v>3819</v>
+        <v>1501</v>
       </c>
       <c r="D80">
-        <v>55.67463620145908</v>
+        <v>33.39904110707697</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2022</t>
-        </is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F80">
+        <v>9</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>West Virginia</t>
+          <t>New Hampshire</t>
         </is>
       </c>
       <c r="B81" s="2">
-        <v>44652</v>
+        <v>42826</v>
       </c>
       <c r="C81">
-        <v>1366</v>
+        <v>447</v>
       </c>
       <c r="D81">
-        <v>75.844688289991</v>
+        <v>32.5760198225445</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2022</t>
-        </is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="F81">
+        <v>7</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>District of Columbia</t>
+          <t>Massachusetts</t>
         </is>
       </c>
       <c r="B82" s="2">
-        <v>45017</v>
+        <v>43922</v>
       </c>
       <c r="C82">
-        <v>603</v>
+        <v>2244</v>
       </c>
       <c r="D82">
-        <v>88.26706716201619</v>
+        <v>32.0945008561394</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F82">
+        <v>10</v>
       </c>
     </row>
     <row r="83">
@@ -2096,606 +2344,693 @@
         </is>
       </c>
       <c r="B83" s="2">
-        <v>45017</v>
+        <v>42826</v>
       </c>
       <c r="C83">
-        <v>564</v>
+        <v>313</v>
       </c>
       <c r="D83">
-        <v>57.44012579794927</v>
+        <v>31.87723293396829</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="F83">
+        <v>8</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Kentucky</t>
+          <t>New Hampshire</t>
         </is>
       </c>
       <c r="B84" s="2">
-        <v>45017</v>
+        <v>43556</v>
       </c>
       <c r="C84">
-        <v>2341</v>
+        <v>437</v>
       </c>
       <c r="D84">
-        <v>52.09004345880559</v>
+        <v>31.84724980414306</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="F84">
+        <v>7</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Louisiana</t>
+          <t>Kentucky</t>
         </is>
       </c>
       <c r="B85" s="2">
-        <v>45017</v>
+        <v>45748</v>
       </c>
       <c r="C85">
-        <v>2319</v>
+        <v>1426</v>
       </c>
       <c r="D85">
-        <v>49.79274494584314</v>
+        <v>31.73020161138691</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F85">
+        <v>10</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Maine</t>
+          <t>Massachusetts</t>
         </is>
       </c>
       <c r="B86" s="2">
-        <v>45017</v>
+        <v>43556</v>
       </c>
       <c r="C86">
-        <v>697</v>
+        <v>2217</v>
       </c>
       <c r="D86">
-        <v>51.36156033030567</v>
+        <v>31.70833707578478</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="F86">
+        <v>8</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>New Mexico</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="B87" s="2">
-        <v>45017</v>
+        <v>43556</v>
       </c>
       <c r="C87">
-        <v>975</v>
+        <v>345</v>
       </c>
       <c r="D87">
-        <v>46.22241943787849</v>
+        <v>31.59488217856329</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="F87">
+        <v>9</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>Kentucky</t>
         </is>
       </c>
       <c r="B88" s="2">
-        <v>45017</v>
+        <v>43191</v>
       </c>
       <c r="C88">
-        <v>5206</v>
+        <v>1418</v>
       </c>
       <c r="D88">
-        <v>44.2313853710003</v>
+        <v>31.55219206517998</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="F88">
+        <v>8</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>South Carolina</t>
+          <t>New Hampshire</t>
         </is>
       </c>
       <c r="B89" s="2">
-        <v>45017</v>
+        <v>42461</v>
       </c>
       <c r="C89">
-        <v>2309</v>
+        <v>430</v>
       </c>
       <c r="D89">
-        <v>45.46257331553684</v>
+        <v>31.33711079126205</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F89">
+        <v>2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Tennessee</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="B90" s="2">
-        <v>45017</v>
+        <v>42826</v>
       </c>
       <c r="C90">
-        <v>3878</v>
+        <v>339</v>
       </c>
       <c r="D90">
-        <v>56.53475757770577</v>
+        <v>31.04540596676219</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="F90">
+        <v>9</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>West Virginia</t>
+          <t>Massachusetts</t>
         </is>
       </c>
       <c r="B91" s="2">
-        <v>45017</v>
+        <v>42826</v>
       </c>
       <c r="C91">
-        <v>1372</v>
+        <v>2168</v>
       </c>
       <c r="D91">
-        <v>76.17782747720911</v>
+        <v>31.00752132625233</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="F91">
+        <v>10</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Alaska</t>
+          <t>Massachusetts</t>
         </is>
       </c>
       <c r="B92" s="2">
-        <v>45383</v>
+        <v>43191</v>
       </c>
       <c r="C92">
-        <v>390</v>
+        <v>2166</v>
       </c>
       <c r="D92">
-        <v>52.99265847862154</v>
+        <v>30.97891660178162</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="F92">
+        <v>9</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>District of Columbia</t>
+          <t>Ohio</t>
         </is>
       </c>
       <c r="B93" s="2">
-        <v>45383</v>
+        <v>42461</v>
       </c>
       <c r="C93">
-        <v>588</v>
+        <v>3575</v>
       </c>
       <c r="D93">
-        <v>86.07136897390632</v>
+        <v>30.37403048431158</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F93">
+        <v>3</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Delaware</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="B94" s="2">
-        <v>45383</v>
+        <v>42461</v>
       </c>
       <c r="C94">
-        <v>473</v>
+        <v>328</v>
       </c>
       <c r="D94">
-        <v>48.1723040823227</v>
+        <v>30.0380329117935</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F94">
+        <v>4</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Louisiana</t>
+          <t>New Jersey</t>
         </is>
       </c>
       <c r="B95" s="2">
-        <v>45383</v>
+        <v>43556</v>
       </c>
       <c r="C95">
-        <v>2079</v>
+        <v>2771</v>
       </c>
       <c r="D95">
-        <v>44.63955012609223</v>
+        <v>30.00858563937022</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="F95">
+        <v>10</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>New Mexico</t>
+          <t>Maine</t>
         </is>
       </c>
       <c r="B96" s="2">
-        <v>45383</v>
+        <v>43191</v>
       </c>
       <c r="C96">
-        <v>933</v>
+        <v>404</v>
       </c>
       <c r="D96">
-        <v>44.23129983132372</v>
+        <v>29.77054572947417</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="F96">
+        <v>10</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Nevada</t>
+          <t>Kentucky</t>
         </is>
       </c>
       <c r="B97" s="2">
-        <v>45383</v>
+        <v>42461</v>
       </c>
       <c r="C97">
-        <v>1440</v>
+        <v>1291</v>
       </c>
       <c r="D97">
-        <v>47.07054501807313</v>
+        <v>28.72629051914481</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F97">
+        <v>5</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Oregon</t>
+          <t>New Hampshire</t>
         </is>
       </c>
       <c r="B98" s="2">
-        <v>45383</v>
+        <v>42095</v>
       </c>
       <c r="C98">
-        <v>1902</v>
+        <v>394</v>
       </c>
       <c r="D98">
-        <v>45.20846163591406</v>
+        <v>28.71353872501685</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="F98">
+        <v>2</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Tennessee</t>
+          <t>Pennsylvania</t>
         </is>
       </c>
       <c r="B99" s="2">
-        <v>45383</v>
+        <v>42461</v>
       </c>
       <c r="C99">
-        <v>3385</v>
+        <v>3601</v>
       </c>
       <c r="D99">
-        <v>49.34764167110212</v>
+        <v>27.76267958814709</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F99">
+        <v>6</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Massachusetts</t>
         </is>
       </c>
       <c r="B100" s="2">
-        <v>45383</v>
+        <v>42461</v>
       </c>
       <c r="C100">
-        <v>3527</v>
+        <v>1889</v>
       </c>
       <c r="D100">
-        <v>46.3021066080077</v>
+        <v>27.01716226258794</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F100">
+        <v>7</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>West Virginia</t>
+          <t>Kentucky</t>
         </is>
       </c>
       <c r="B101" s="2">
-        <v>45383</v>
+        <v>42095</v>
       </c>
       <c r="C101">
-        <v>1232</v>
+        <v>1172</v>
       </c>
       <c r="D101">
-        <v>68.40457977545309</v>
+        <v>26.07839851931659</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="F101">
+        <v>3</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Alaska</t>
+          <t>District of Columbia</t>
         </is>
       </c>
       <c r="B102" s="2">
-        <v>45748</v>
+        <v>42461</v>
       </c>
       <c r="C102">
-        <v>334</v>
+        <v>174</v>
       </c>
       <c r="D102">
-        <v>45.38345623553742</v>
+        <v>25.47009898207432</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F102">
+        <v>8</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Arizona</t>
+          <t>New Mexico</t>
         </is>
       </c>
       <c r="B103" s="2">
-        <v>45748</v>
+        <v>42095</v>
       </c>
       <c r="C103">
-        <v>2790</v>
+        <v>536</v>
       </c>
       <c r="D103">
-        <v>39.41121620611812</v>
+        <v>25.4104787884132</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="F103">
+        <v>4</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>District of Columbia</t>
+          <t>Ohio</t>
         </is>
       </c>
       <c r="B104" s="2">
-        <v>45748</v>
+        <v>42095</v>
       </c>
       <c r="C104">
-        <v>360</v>
+        <v>2955</v>
       </c>
       <c r="D104">
-        <v>52.69675651463653</v>
+        <v>25.10636645626314</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="F104">
+        <v>5</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Delaware</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="B105" s="2">
-        <v>45748</v>
+        <v>42095</v>
       </c>
       <c r="C105">
-        <v>356</v>
+        <v>267</v>
       </c>
       <c r="D105">
-        <v>36.25653330508855</v>
+        <v>24.45169142514898</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="F105">
+        <v>6</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Kentucky</t>
+          <t>Connecticut</t>
         </is>
       </c>
       <c r="B106" s="2">
-        <v>45748</v>
+        <v>42461</v>
       </c>
       <c r="C106">
-        <v>1426</v>
+        <v>869</v>
       </c>
       <c r="D106">
-        <v>31.73020161138691</v>
+        <v>24.10320275813864</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F106">
+        <v>9</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>New Mexico</t>
+          <t>Maryland</t>
         </is>
       </c>
       <c r="B107" s="2">
-        <v>45748</v>
+        <v>42461</v>
       </c>
       <c r="C107">
-        <v>824</v>
+        <v>1479</v>
       </c>
       <c r="D107">
-        <v>39.06387037621731</v>
+        <v>24.05447142372708</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F107">
+        <v>10</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Nevada</t>
+          <t>Pennsylvania</t>
         </is>
       </c>
       <c r="B108" s="2">
-        <v>45748</v>
+        <v>42095</v>
       </c>
       <c r="C108">
-        <v>1386</v>
+        <v>2862</v>
       </c>
       <c r="D108">
-        <v>45.30539957989539</v>
+        <v>22.06520105006303</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="F108">
+        <v>7</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Tennessee</t>
+          <t>Delaware</t>
         </is>
       </c>
       <c r="B109" s="2">
-        <v>45748</v>
+        <v>42095</v>
       </c>
       <c r="C109">
-        <v>2361</v>
+        <v>200</v>
       </c>
       <c r="D109">
-        <v>34.41943337827832</v>
+        <v>20.368838935443</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="F109">
+        <v>8</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Massachusetts</t>
         </is>
       </c>
       <c r="B110" s="2">
-        <v>45748</v>
+        <v>42095</v>
       </c>
       <c r="C110">
-        <v>3227</v>
+        <v>1376</v>
       </c>
       <c r="D110">
-        <v>42.36373632663478</v>
+        <v>19.68005043585019</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="F110">
+        <v>9</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>West Virginia</t>
+          <t>Wyoming</t>
         </is>
       </c>
       <c r="B111" s="2">
-        <v>45748</v>
+        <v>42095</v>
       </c>
       <c r="C111">
-        <v>729</v>
+        <v>112</v>
       </c>
       <c r="D111">
-        <v>40.47641124700105</v>
+        <v>19.42282980225131</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="F111">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
